--- a/artefakti/so4-risk/Шаблон - час 4 Оценка на риска.xlsx
+++ b/artefakti/so4-risk/Шаблон - час 4 Оценка на риска.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Инструкции" sheetId="1" state="visible" r:id="rId3"/>
@@ -123,7 +123,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="469" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="311">
   <si>
     <t xml:space="preserve">МИС — инструмент за риска (инвентаризация, оценка на риска, план за третиране)</t>
   </si>
@@ -1053,6 +1053,9 @@
   </si>
   <si>
     <t xml:space="preserve">artefakti/h13-wazuh/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">,</t>
   </si>
 </sst>
 </file>
@@ -2456,7 +2459,9 @@
       </c>
       <c r="D11" s="16"/>
       <c r="E11" s="16"/>
-      <c r="F11" s="16"/>
+      <c r="F11" s="16" t="s">
+        <v>103</v>
+      </c>
       <c r="G11" s="16" t="s">
         <v>104</v>
       </c>
@@ -2476,9 +2481,15 @@
       <c r="C12" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="D12" s="16"/>
-      <c r="E12" s="16"/>
-      <c r="F12" s="16"/>
+      <c r="D12" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="E12" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="F12" s="16" t="s">
+        <v>103</v>
+      </c>
       <c r="G12" s="16" t="s">
         <v>134</v>
       </c>
@@ -2498,8 +2509,12 @@
       <c r="C13" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
+      <c r="D13" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="E13" s="16" t="s">
+        <v>98</v>
+      </c>
       <c r="F13" s="16" t="s">
         <v>103</v>
       </c>
@@ -12706,7 +12721,9 @@
       <c r="J18" s="16"/>
       <c r="K18" s="16"/>
       <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
+      <c r="M18" s="16" t="s">
+        <v>310</v>
+      </c>
       <c r="N18" s="21" t="str">
         <f aca="false">IF(OR(L18="",M18=""),"",L18*M18)</f>
         <v/>
